--- a/assets/database_structure/vessel_list.xlsx
+++ b/assets/database_structure/vessel_list.xlsx
@@ -1673,11 +1673,14 @@
   <cols>
     <col min="1" max="1" width="20.0588235294118" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.8235294117647" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="8" width="11.3308823529412" style="1"/>
-    <col min="9" max="9" width="8.17647058823529" style="1" customWidth="1"/>
-    <col min="10" max="10" width="5.76470588235294" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.3308823529412" style="1"/>
+    <col min="3" max="3" width="10.1764705882353" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3308823529412" style="1"/>
+    <col min="5" max="5" width="13.5882352941176" style="1" customWidth="1"/>
+    <col min="6" max="8" width="11.3308823529412" style="1"/>
+    <col min="9" max="9" width="10.1764705882353" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.2941176470588" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.4117647058824" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.3308823529412" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.8" spans="1:11">
